--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -603,12 +603,8 @@
       <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
       <c r="F2" s="10" t="s">
         <v>8</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -603,8 +603,12 @@
       <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="D2" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0</v>
+      </c>
       <c r="F2" s="10" t="s">
         <v>8</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -623,8 +623,12 @@
       <c r="C3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="D3" s="6">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1</v>
+      </c>
       <c r="F3" s="10" t="s">
         <v>10</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -707,8 +707,12 @@
       <c r="C8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
       <c r="F8" s="10" t="s">
         <v>13</v>
       </c>
@@ -899,8 +903,12 @@
       <c r="C20" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
+      <c r="D20" s="6">
+        <v>4</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1</v>
+      </c>
       <c r="F20" s="10" t="s">
         <v>23</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -727,8 +727,12 @@
       <c r="C9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
       <c r="F9" s="10" t="s">
         <v>15</v>
       </c>
@@ -807,8 +811,12 @@
       <c r="C14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1</v>
+      </c>
       <c r="F14" s="10" t="s">
         <v>18</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -831,8 +831,12 @@
       <c r="C15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1</v>
+      </c>
       <c r="F15" s="10" t="s">
         <v>20</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -935,8 +935,12 @@
       <c r="C21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6"/>
+      <c r="D21" s="5">
+        <v>2</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0</v>
+      </c>
       <c r="F21" s="11" t="s">
         <v>25</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1019,8 +1019,12 @@
       <c r="C26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="6"/>
+      <c r="D26" s="5">
+        <v>7</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1</v>
+      </c>
       <c r="F26" s="11" t="s">
         <v>28</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1039,8 +1039,12 @@
       <c r="C27" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="6"/>
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0</v>
+      </c>
       <c r="F27" s="11" t="s">
         <v>30</v>
       </c>
@@ -1119,8 +1123,12 @@
       <c r="C32" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="6"/>
+      <c r="D32" s="5">
+        <v>2</v>
+      </c>
+      <c r="E32" s="6">
+        <v>2</v>
+      </c>
       <c r="F32" s="11" t="s">
         <v>33</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1143,8 +1143,12 @@
       <c r="C33" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="6"/>
+      <c r="D33" s="5">
+        <v>5</v>
+      </c>
+      <c r="E33" s="6">
+        <v>1</v>
+      </c>
       <c r="F33" s="11" t="s">
         <v>35</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1323,8 +1323,12 @@
       <c r="C44" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D44" s="5"/>
-      <c r="E44" s="6"/>
+      <c r="D44" s="5">
+        <v>0</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0</v>
+      </c>
       <c r="F44" s="11" t="s">
         <v>43</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1227,8 +1227,12 @@
       <c r="C38" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="6"/>
+      <c r="D38" s="5">
+        <v>1</v>
+      </c>
+      <c r="E38" s="6">
+        <v>1</v>
+      </c>
       <c r="F38" s="11" t="s">
         <v>38</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1347,8 +1347,12 @@
       <c r="C45" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D45" s="5"/>
-      <c r="E45" s="6"/>
+      <c r="D45" s="5">
+        <v>1</v>
+      </c>
+      <c r="E45" s="6">
+        <v>1</v>
+      </c>
       <c r="F45" s="11" t="s">
         <v>45</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1247,8 +1247,12 @@
       <c r="C39" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="6"/>
+      <c r="D39" s="5">
+        <v>2</v>
+      </c>
+      <c r="E39" s="6">
+        <v>2</v>
+      </c>
       <c r="F39" s="11" t="s">
         <v>40</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1435,8 +1435,12 @@
       <c r="C50" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D50" s="5"/>
-      <c r="E50" s="6"/>
+      <c r="D50" s="5">
+        <v>3</v>
+      </c>
+      <c r="E50" s="6">
+        <v>1</v>
+      </c>
       <c r="F50" s="11" t="s">
         <v>48</v>
       </c>
@@ -1451,8 +1455,12 @@
       <c r="C51" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D51" s="5"/>
-      <c r="E51" s="6"/>
+      <c r="D51" s="5">
+        <v>1</v>
+      </c>
+      <c r="E51" s="6">
+        <v>4</v>
+      </c>
       <c r="F51" s="11" t="s">
         <v>50</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1565,8 +1565,12 @@
       <c r="C56" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D56" s="5"/>
-      <c r="E56" s="6"/>
+      <c r="D56" s="5">
+        <v>3</v>
+      </c>
+      <c r="E56" s="6">
+        <v>0</v>
+      </c>
       <c r="F56" s="10" t="s">
         <v>63</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1590,8 +1590,12 @@
       <c r="C57" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
+      <c r="D57" s="6">
+        <v>3</v>
+      </c>
+      <c r="E57" s="6">
+        <v>1</v>
+      </c>
       <c r="F57" s="10" t="s">
         <v>67</v>
       </c>
@@ -1695,8 +1699,12 @@
       <c r="C62" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
+      <c r="D62" s="6">
+        <v>1</v>
+      </c>
+      <c r="E62" s="6">
+        <v>1</v>
+      </c>
       <c r="F62" s="10" t="s">
         <v>55</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1829,8 +1829,12 @@
       <c r="C68" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
+      <c r="D68" s="6">
+        <v>4</v>
+      </c>
+      <c r="E68" s="6">
+        <v>2</v>
+      </c>
       <c r="F68" s="10" t="s">
         <v>65</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1854,8 +1854,12 @@
       <c r="C69" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
+      <c r="D69" s="6">
+        <v>1</v>
+      </c>
+      <c r="E69" s="6">
+        <v>0</v>
+      </c>
       <c r="F69" s="10" t="s">
         <v>53</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1724,8 +1724,12 @@
       <c r="C63" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
+      <c r="D63" s="6">
+        <v>1</v>
+      </c>
+      <c r="E63" s="6">
+        <v>3</v>
+      </c>
       <c r="F63" s="10" t="s">
         <v>59</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -643,8 +643,12 @@
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+      <c r="D4" s="6">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
       <c r="F4" s="10" t="s">
         <v>9</v>
       </c>
@@ -659,8 +663,12 @@
       <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
       <c r="F5" s="10" t="s">
         <v>8</v>
       </c>
@@ -747,8 +755,12 @@
       <c r="C10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="D10" s="6">
+        <v>6</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
       <c r="F10" s="10" t="s">
         <v>14</v>
       </c>
@@ -763,8 +775,12 @@
       <c r="C11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="D11" s="6">
+        <v>4</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
       <c r="F11" s="10" t="s">
         <v>13</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -883,8 +883,12 @@
       <c r="C17" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
+      <c r="D17" s="6">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1</v>
+      </c>
       <c r="F17" s="10" t="s">
         <v>18</v>
       </c>
@@ -971,8 +975,12 @@
       <c r="C22" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
+      <c r="D22" s="6">
+        <v>2</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0</v>
+      </c>
       <c r="F22" s="10" t="s">
         <v>24</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -867,8 +867,12 @@
       <c r="C16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="D16" s="6">
+        <v>3</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
       <c r="F16" s="10" t="s">
         <v>19</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -999,8 +999,12 @@
       <c r="C23" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
+      <c r="D23" s="6">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1</v>
+      </c>
       <c r="F23" s="10" t="s">
         <v>23</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1091,8 +1091,12 @@
       <c r="C28" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
+      <c r="D28" s="6">
+        <v>2</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1</v>
+      </c>
       <c r="F28" s="10" t="s">
         <v>29</v>
       </c>
@@ -1107,8 +1111,12 @@
       <c r="C29" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
+      <c r="D29" s="6">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
       <c r="F29" s="10" t="s">
         <v>28</v>
       </c>
@@ -1195,8 +1203,12 @@
       <c r="C34" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
+      <c r="D34" s="6">
+        <v>5</v>
+      </c>
+      <c r="E34" s="6">
+        <v>1</v>
+      </c>
       <c r="F34" s="10" t="s">
         <v>34</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1223,8 +1223,12 @@
       <c r="C35" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+      <c r="D35" s="6">
+        <v>0</v>
+      </c>
+      <c r="E35" s="6">
+        <v>4</v>
+      </c>
       <c r="F35" s="10" t="s">
         <v>33</v>
       </c>
@@ -1311,8 +1315,12 @@
       <c r="C40" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
+      <c r="D40" s="6">
+        <v>0</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0</v>
+      </c>
       <c r="F40" s="10" t="s">
         <v>39</v>
       </c>
@@ -1327,8 +1335,12 @@
       <c r="C41" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
+      <c r="D41" s="6">
+        <v>1</v>
+      </c>
+      <c r="E41" s="6">
+        <v>3</v>
+      </c>
       <c r="F41" s="10" t="s">
         <v>38</v>
       </c>
@@ -1415,8 +1427,12 @@
       <c r="C46" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
+      <c r="D46" s="6">
+        <v>4</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0</v>
+      </c>
       <c r="F46" s="10" t="s">
         <v>44</v>
       </c>
@@ -1431,8 +1447,12 @@
       <c r="C47" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
+      <c r="D47" s="6">
+        <v>2</v>
+      </c>
+      <c r="E47" s="6">
+        <v>2</v>
+      </c>
       <c r="F47" s="10" t="s">
         <v>43</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1544,8 +1544,12 @@
       <c r="C52" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D52" s="5"/>
-      <c r="E52" s="6"/>
+      <c r="D52" s="5">
+        <v>3</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0</v>
+      </c>
       <c r="F52" s="11" t="s">
         <v>49</v>
       </c>
@@ -1565,8 +1569,12 @@
       <c r="C53" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D53" s="5"/>
-      <c r="E53" s="6"/>
+      <c r="D53" s="5">
+        <v>3</v>
+      </c>
+      <c r="E53" s="6">
+        <v>2</v>
+      </c>
       <c r="F53" s="11" t="s">
         <v>48</v>
       </c>
@@ -1679,8 +1687,12 @@
       <c r="C58" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
+      <c r="D58" s="6">
+        <v>2</v>
+      </c>
+      <c r="E58" s="6">
+        <v>0</v>
+      </c>
       <c r="F58" s="10" t="s">
         <v>64</v>
       </c>
@@ -1700,8 +1712,12 @@
       <c r="C59" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
+      <c r="D59" s="6">
+        <v>1</v>
+      </c>
+      <c r="E59" s="6">
+        <v>2</v>
+      </c>
       <c r="F59" s="10" t="s">
         <v>63</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1829,8 +1829,12 @@
       <c r="C64" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
+      <c r="D64" s="6">
+        <v>5</v>
+      </c>
+      <c r="E64" s="6">
+        <v>0</v>
+      </c>
       <c r="F64" s="10" t="s">
         <v>54</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1967,8 +1967,12 @@
       <c r="C70" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
+      <c r="D70" s="6">
+        <v>0</v>
+      </c>
+      <c r="E70" s="6">
+        <v>0</v>
+      </c>
       <c r="F70" s="10" t="s">
         <v>58</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1992,8 +1992,12 @@
       <c r="C71" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
+      <c r="D71" s="6">
+        <v>0</v>
+      </c>
+      <c r="E71" s="6">
+        <v>1</v>
+      </c>
       <c r="F71" s="10" t="s">
         <v>65</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1854,8 +1854,12 @@
       <c r="C65" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
+      <c r="D65" s="6">
+        <v>1</v>
+      </c>
+      <c r="E65" s="6">
+        <v>0</v>
+      </c>
       <c r="F65" s="10" t="s">
         <v>55</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -683,8 +683,12 @@
       <c r="C6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>3</v>
+      </c>
       <c r="F6" s="10" t="s">
         <v>7</v>
       </c>
@@ -699,8 +703,12 @@
       <c r="C7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="D7" s="6">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
       <c r="F7" s="10" t="s">
         <v>9</v>
       </c>
@@ -795,8 +803,12 @@
       <c r="C12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="D12" s="6">
+        <v>2</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
       <c r="F12" s="10" t="s">
         <v>12</v>
       </c>
@@ -811,8 +823,12 @@
       <c r="C13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="D13" s="6">
+        <v>3</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1</v>
+      </c>
       <c r="F13" s="10" t="s">
         <v>14</v>
       </c>
@@ -907,8 +923,12 @@
       <c r="C18" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
+      <c r="D18" s="6">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3</v>
+      </c>
       <c r="F18" s="10" t="s">
         <v>17</v>
       </c>
@@ -923,8 +943,12 @@
       <c r="C19" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
+      <c r="D19" s="6">
+        <v>4</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2</v>
+      </c>
       <c r="F19" s="10" t="s">
         <v>19</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1043,8 +1043,12 @@
       <c r="C24" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
+      <c r="D24" s="6">
+        <v>3</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2</v>
+      </c>
       <c r="F24" s="10" t="s">
         <v>22</v>
       </c>
@@ -1059,8 +1063,12 @@
       <c r="C25" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
+      <c r="D25" s="6">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0</v>
+      </c>
       <c r="F25" s="10" t="s">
         <v>24</v>
       </c>
@@ -1155,8 +1163,12 @@
       <c r="C30" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
+      <c r="D30" s="6">
+        <v>2</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1</v>
+      </c>
       <c r="F30" s="10" t="s">
         <v>27</v>
       </c>
@@ -1171,8 +1183,12 @@
       <c r="C31" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
+      <c r="D31" s="6">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6">
+        <v>2</v>
+      </c>
       <c r="F31" s="10" t="s">
         <v>29</v>
       </c>
@@ -1267,8 +1283,12 @@
       <c r="C36" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
+      <c r="D36" s="6">
+        <v>1</v>
+      </c>
+      <c r="E36" s="6">
+        <v>3</v>
+      </c>
       <c r="F36" s="10" t="s">
         <v>32</v>
       </c>
@@ -1283,8 +1303,12 @@
       <c r="C37" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
+      <c r="D37" s="6">
+        <v>1</v>
+      </c>
+      <c r="E37" s="6">
+        <v>1</v>
+      </c>
       <c r="F37" s="10" t="s">
         <v>34</v>
       </c>

--- a/Resultados_Reales_Grupos.xlsx
+++ b/Resultados_Reales_Grupos.xlsx
@@ -1403,8 +1403,12 @@
       <c r="C42" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
+      <c r="D42" s="6">
+        <v>1</v>
+      </c>
+      <c r="E42" s="6">
+        <v>5</v>
+      </c>
       <c r="F42" s="10" t="s">
         <v>37</v>
       </c>
@@ -1419,8 +1423,12 @@
       <c r="C43" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
+      <c r="D43" s="6">
+        <v>1</v>
+      </c>
+      <c r="E43" s="6">
+        <v>1</v>
+      </c>
       <c r="F43" s="10" t="s">
         <v>39</v>
       </c>
@@ -1515,8 +1523,12 @@
       <c r="C48" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
+      <c r="D48" s="6">
+        <v>0</v>
+      </c>
+      <c r="E48" s="6">
+        <v>1</v>
+      </c>
       <c r="F48" s="10" t="s">
         <v>42</v>
       </c>
@@ -1531,8 +1543,12 @@
       <c r="C49" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
+      <c r="D49" s="6">
+        <v>0</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0</v>
+      </c>
       <c r="F49" s="10" t="s">
         <v>44</v>
       </c>
@@ -1642,8 +1658,12 @@
       <c r="C54" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
+      <c r="D54" s="6">
+        <v>1</v>
+      </c>
+      <c r="E54" s="6">
+        <v>4</v>
+      </c>
       <c r="F54" s="10" t="s">
         <v>47</v>
       </c>
@@ -1663,8 +1683,12 @@
       <c r="C55" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
+      <c r="D55" s="6">
+        <v>5</v>
+      </c>
+      <c r="E55" s="6">
+        <v>0</v>
+      </c>
       <c r="F55" s="10" t="s">
         <v>49</v>
       </c>
@@ -1785,8 +1809,12 @@
       <c r="C60" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
+      <c r="D60" s="6">
+        <v>3</v>
+      </c>
+      <c r="E60" s="6">
+        <v>3</v>
+      </c>
       <c r="F60" s="10" t="s">
         <v>64</v>
       </c>
@@ -1806,8 +1834,12 @@
       <c r="C61" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
+      <c r="D61" s="6">
+        <v>1</v>
+      </c>
+      <c r="E61" s="6">
+        <v>3</v>
+      </c>
       <c r="F61" s="10" t="s">
         <v>52</v>
       </c>
@@ -1927,8 +1959,12 @@
       <c r="C66" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
+      <c r="D66" s="6">
+        <v>0</v>
+      </c>
+      <c r="E66" s="6">
+        <v>0</v>
+      </c>
       <c r="F66" s="10" t="s">
         <v>57</v>
       </c>
@@ -1948,8 +1984,12 @@
       <c r="C67" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
+      <c r="D67" s="6">
+        <v>3</v>
+      </c>
+      <c r="E67" s="6">
+        <v>1</v>
+      </c>
       <c r="F67" s="10" t="s">
         <v>54</v>
       </c>
@@ -2069,8 +2109,12 @@
       <c r="C72" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
+      <c r="D72" s="6">
+        <v>0</v>
+      </c>
+      <c r="E72" s="6">
+        <v>2</v>
+      </c>
       <c r="F72" s="10" t="s">
         <v>62</v>
       </c>
@@ -2090,8 +2134,12 @@
       <c r="C73" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
+      <c r="D73" s="6">
+        <v>2</v>
+      </c>
+      <c r="E73" s="6">
+        <v>1</v>
+      </c>
       <c r="F73" s="10" t="s">
         <v>58</v>
       </c>
